--- a/datosNivelesCorValues.xlsx
+++ b/datosNivelesCorValues.xlsx
@@ -528,10 +528,10 @@
         <v>0.08181428472817881</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.002231232344050298</v>
+        <v>-0.003802836692310912</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.03674620931561183</v>
+        <v>0.0556403973317163</v>
       </c>
       <c r="F2" t="n">
         <v>0.2146685986275435</v>
@@ -586,10 +586,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1170014494130177</v>
+        <v>-0.1197425588562596</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1360369683546246</v>
+        <v>-0.0891183678845299</v>
       </c>
       <c r="F3" t="n">
         <v>0.03691504477982212</v>
@@ -638,55 +638,55 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.002231232344050298</v>
+        <v>-0.003802836692310912</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1170014494130177</v>
+        <v>-0.1197425588562596</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.257908750775264</v>
+        <v>0.8171090728926109</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6809436419138201</v>
+        <v>0.6790823289635499</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6541028263804571</v>
+        <v>0.6523156071281279</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5662857285886342</v>
+        <v>0.5647356680345048</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7327305592185771</v>
+        <v>0.7297033570561771</v>
       </c>
       <c r="J4" t="n">
-        <v>0.719651223460939</v>
+        <v>0.7162681635378394</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2603645261892509</v>
+        <v>0.2614286911514148</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5694294884036952</v>
+        <v>0.568639655862731</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4882846679554995</v>
+        <v>0.4883482554913657</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5452909987019283</v>
+        <v>0.5431880749680327</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8886932190589768</v>
+        <v>0.8863239700837817</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8126739899325457</v>
+        <v>0.8101240182794622</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2746486065603303</v>
+        <v>0.2759892370026096</v>
       </c>
       <c r="R4" t="n">
-        <v>0.282448410141744</v>
+        <v>0.2837924453699338</v>
       </c>
     </row>
     <row r="5">
@@ -696,55 +696,55 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.03674620931561183</v>
+        <v>0.0556403973317163</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1360369683546246</v>
+        <v>-0.0891183678845299</v>
       </c>
       <c r="D5" t="n">
-        <v>0.257908750775264</v>
+        <v>0.8171090728926109</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1640605713260567</v>
+        <v>0.6781232278611986</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1660088520862688</v>
+        <v>0.6703223229324553</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1114375588114762</v>
+        <v>0.5077093073120678</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1213596304774282</v>
+        <v>0.6957847763196943</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1092725450569894</v>
+        <v>0.6972384931462772</v>
       </c>
       <c r="K5" t="n">
-        <v>0.09491443991410523</v>
+        <v>0.1748099855838134</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1784914270567395</v>
+        <v>0.592451611586621</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1963129079132234</v>
+        <v>0.5401100612857738</v>
       </c>
       <c r="N5" t="n">
-        <v>0.09230301624725298</v>
+        <v>0.5090225850788819</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1850511830898595</v>
+        <v>0.8141145767092343</v>
       </c>
       <c r="P5" t="n">
-        <v>0.163713160365208</v>
+        <v>0.7659617432467938</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1767294165514525</v>
+        <v>0.3380109721027198</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1681814037748048</v>
+        <v>0.3200564777884227</v>
       </c>
     </row>
     <row r="6">
@@ -760,10 +760,10 @@
         <v>0.03691504477982212</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6809436419138201</v>
+        <v>0.6790823289635499</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1640605713260567</v>
+        <v>0.6781232278611986</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -818,10 +818,10 @@
         <v>0.04871115143481359</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6541028263804571</v>
+        <v>0.6523156071281279</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1660088520862688</v>
+        <v>0.6703223229324553</v>
       </c>
       <c r="F7" t="n">
         <v>0.977645246815116</v>
@@ -876,10 +876,10 @@
         <v>-0.008665571202553859</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5662857285886342</v>
+        <v>0.5647356680345048</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1114375588114762</v>
+        <v>0.5077093073120678</v>
       </c>
       <c r="F8" t="n">
         <v>0.7809326298597665</v>
@@ -934,10 +934,10 @@
         <v>0.004432022348586862</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7327305592185771</v>
+        <v>0.7297033570561771</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1213596304774282</v>
+        <v>0.6957847763196943</v>
       </c>
       <c r="F9" t="n">
         <v>0.9176867728093996</v>
@@ -992,10 +992,10 @@
         <v>0.02034100732939796</v>
       </c>
       <c r="D10" t="n">
-        <v>0.719651223460939</v>
+        <v>0.7162681635378394</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1092725450569894</v>
+        <v>0.6972384931462772</v>
       </c>
       <c r="F10" t="n">
         <v>0.9118444394700249</v>
@@ -1050,10 +1050,10 @@
         <v>-0.08189040679484891</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2603645261892509</v>
+        <v>0.2614286911514148</v>
       </c>
       <c r="E11" t="n">
-        <v>0.09491443991410523</v>
+        <v>0.1748099855838134</v>
       </c>
       <c r="F11" t="n">
         <v>0.2710700551438288</v>
@@ -1108,10 +1108,10 @@
         <v>0.05728290462682773</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5694294884036952</v>
+        <v>0.568639655862731</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1784914270567395</v>
+        <v>0.592451611586621</v>
       </c>
       <c r="F12" t="n">
         <v>0.9547643726053725</v>
@@ -1166,10 +1166,10 @@
         <v>0.06916817750602999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4882846679554995</v>
+        <v>0.4883482554913657</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1963129079132234</v>
+        <v>0.5401100612857738</v>
       </c>
       <c r="F13" t="n">
         <v>0.8913826058207561</v>
@@ -1224,10 +1224,10 @@
         <v>0.01841579138264593</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5452909987019283</v>
+        <v>0.5431880749680327</v>
       </c>
       <c r="E14" t="n">
-        <v>0.09230301624725298</v>
+        <v>0.5090225850788819</v>
       </c>
       <c r="F14" t="n">
         <v>0.7822016968759629</v>
@@ -1282,10 +1282,10 @@
         <v>0.007951463957021239</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8886932190589768</v>
+        <v>0.8863239700837817</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1850511830898595</v>
+        <v>0.8141145767092343</v>
       </c>
       <c r="F15" t="n">
         <v>0.8154053913032333</v>
@@ -1340,10 +1340,10 @@
         <v>0.01708722552571064</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8126739899325457</v>
+        <v>0.8101240182794622</v>
       </c>
       <c r="E16" t="n">
-        <v>0.163713160365208</v>
+        <v>0.7659617432467938</v>
       </c>
       <c r="F16" t="n">
         <v>0.8271016311973716</v>
@@ -1398,10 +1398,10 @@
         <v>0.0373367864104058</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2746486065603303</v>
+        <v>0.2759892370026096</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1767294165514525</v>
+        <v>0.3380109721027198</v>
       </c>
       <c r="F17" t="n">
         <v>0.0753904270469026</v>
@@ -1456,10 +1456,10 @@
         <v>0.06730363258409847</v>
       </c>
       <c r="D18" t="n">
-        <v>0.282448410141744</v>
+        <v>0.2837924453699338</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1681814037748048</v>
+        <v>0.3200564777884227</v>
       </c>
       <c r="F18" t="n">
         <v>0.106579192378614</v>
